--- a/ebid-lcs-automation/src/test/resources/testdata/Global_TestData.xlsx
+++ b/ebid-lcs-automation/src/test/resources/testdata/Global_TestData.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="13"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="15"/>
   </bookViews>
   <sheets>
     <sheet name="AddFollowUP1" sheetId="1" state="visible" r:id="rId3"/>
@@ -22,6 +22,8 @@
     <sheet name="SiteVisit" sheetId="12" state="visible" r:id="rId14"/>
     <sheet name="Remedial" sheetId="13" state="visible" r:id="rId15"/>
     <sheet name="LegalOrder" sheetId="14" state="visible" r:id="rId16"/>
+    <sheet name="Calendar" sheetId="15" state="visible" r:id="rId17"/>
+    <sheet name="Sheet16" sheetId="16" state="visible" r:id="rId18"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -33,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1378" uniqueCount="580">
   <si>
     <t xml:space="preserve">Comm type</t>
   </si>
@@ -938,15 +940,18 @@
     <t xml:space="preserve">actionName</t>
   </si>
   <si>
-    <t xml:space="preserve">Asset Repossession</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select Asset Repossession</t>
+    <t xml:space="preserve">Asset Repossession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Asset Repossession session</t>
   </si>
   <si>
     <t xml:space="preserve">DU_02</t>
   </si>
   <si>
+    <t xml:space="preserve">Promise To Pay </t>
+  </si>
+  <si>
     <t xml:space="preserve">Promise To Pay</t>
   </si>
   <si>
@@ -1163,72 +1168,102 @@
     <t xml:space="preserve">Follow up test remark</t>
   </si>
   <si>
+    <t xml:space="preserve">FIELD_NAME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">INPUT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXPECTED</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DESCRIPTION</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CHECK_TYPE</t>
+  </si>
+  <si>
     <t xml:space="preserve">DL_01</t>
   </si>
   <si>
-    <t xml:space="preserve">noticeType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">First Notice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select First Notice</t>
+    <t xml:space="preserve">demandLetterType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">First Demand Letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select demand letter type</t>
   </si>
   <si>
     <t xml:space="preserve">DL_02</t>
   </si>
   <si>
-    <t xml:space="preserve">Final Notice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Select Final Notice</t>
+    <t xml:space="preserve">Second Demand Letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select second option</t>
   </si>
   <si>
     <t xml:space="preserve">DL_03</t>
   </si>
   <si>
-    <t xml:space="preserve">issuanceDate</t>
+    <t xml:space="preserve">Third Demand Letter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select third option</t>
   </si>
   <si>
     <t xml:space="preserve">DL_04</t>
   </si>
   <si>
+    <t xml:space="preserve">sendingDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter sending date</t>
+  </si>
+  <si>
     <t xml:space="preserve">DL_05</t>
   </si>
   <si>
+    <t xml:space="preserve">Empty date validation</t>
+  </si>
+  <si>
     <t xml:space="preserve">DL_06</t>
   </si>
   <si>
+    <t xml:space="preserve">userName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TestUser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter user name</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Empty name validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DL_08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reminderType</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call Reminder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visit Reminder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">reminderDate</t>
+  </si>
+  <si>
     <t xml:space="preserve">Invalid day</t>
   </si>
   <si>
-    <t xml:space="preserve">DL_07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">userName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TestUser</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter username</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DL_08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reminderType</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Call Reminder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visit Reminder</t>
-  </si>
-  <si>
-    <t xml:space="preserve">reminderDate</t>
-  </si>
-  <si>
     <t xml:space="preserve">RM_06</t>
   </si>
   <si>
@@ -1398,15 +1433,359 @@
   </si>
   <si>
     <t xml:space="preserve">Legal order final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAL_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">checkbox</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PTP checkbox default selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAL_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Visited checkbox default selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAL_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next Court Case checkbox default selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAL_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Next Hearing checkbox default selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAL_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Call checkbox default selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAL_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MAIL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mail checkbox default selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CAL_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SITE VISIT</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Site Visit checkbox default selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter numeric value</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter alphabets - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter special chars - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter alphanumeric - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter negative - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter decimal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter spaces only - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter leading zeros</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final value for save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter valid date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025/12/19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter invalid format - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter day 32 - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter month 13 - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter non-leap 29 Feb - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter leap year 29 Feb</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter far future - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter old past - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter spaces - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downpayment test remark</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter special chars</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter alphanumeric</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_27</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downpayment validation test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Downpayment + Schedule PTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select schedule type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter valid plan date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_32</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_33</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_34</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter non-leap - reject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_35</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter leap year</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_36</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final plan date for save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_37</t>
+  </si>
+  <si>
+    <t xml:space="preserve">paymentMode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cheque</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Cheque payment mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_38</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select CASH payment mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_39</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Account Transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_40</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bank Transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Bank Transfer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_41</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Visa Swipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Select Visa Swipe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_42</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final payment mode for save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_43</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chequeDate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter valid cheque date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_44</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_45</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_46</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final cheque date for save</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_47</t>
+  </si>
+  <si>
+    <t xml:space="preserve">chequeNumber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_48</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter alphabets - check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_49</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter special chars - check</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_50</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DP_51</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final cheque number for save</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="@"/>
+    <numFmt numFmtId="166" formatCode="dd/mm/yy"/>
+    <numFmt numFmtId="167" formatCode="&quot;TRUE&quot;;&quot;TRUE&quot;;&quot;FALSE&quot;"/>
   </numFmts>
   <fonts count="7">
     <font>
@@ -1521,7 +1900,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1602,12 +1981,20 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -1618,12 +2005,16 @@
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -2205,187 +2596,185 @@
   <dimension ref="A1:F9"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.22"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="21.7"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="18.36"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.59"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="21.7"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="24" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>178</v>
-      </c>
-      <c r="C1" s="22" t="s">
-        <v>179</v>
-      </c>
-      <c r="D1" s="22" t="s">
-        <v>180</v>
-      </c>
-      <c r="E1" s="22" t="s">
-        <v>181</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>182</v>
+      <c r="B1" s="24" t="s">
+        <v>377</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>380</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>381</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
-        <v>376</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>377</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>378</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>379</v>
-      </c>
-      <c r="F2" s="23" t="s">
+      <c r="A2" s="25" t="s">
+        <v>382</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="C2" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="D2" s="25" t="s">
+        <v>384</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>385</v>
+      </c>
+      <c r="F2" s="25" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>380</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>377</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>381</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>381</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>382</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
+      <c r="A3" s="25" t="s">
+        <v>386</v>
+      </c>
+      <c r="B3" s="25" t="s">
         <v>383</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
-        <v>385</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>214</v>
-      </c>
-      <c r="D5" s="23" t="s">
+      <c r="C3" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>387</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>388</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="25" t="s">
+        <v>389</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>383</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>390</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>391</v>
+      </c>
+      <c r="F4" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
+        <v>392</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C5" s="26" t="n">
+        <v>46153</v>
+      </c>
+      <c r="D5" s="26" t="n">
+        <v>46153</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>394</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="s">
+        <v>395</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>393</v>
+      </c>
+      <c r="C6" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="E5" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="23" t="s">
+      <c r="D6" s="25" t="s">
+        <v>396</v>
+      </c>
+      <c r="E6" s="25" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
-        <v>386</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>192</v>
-      </c>
-      <c r="D6" s="23" t="s">
+      <c r="F6" s="27"/>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25" t="s">
+        <v>397</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="C7" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="D7" s="25" t="s">
+        <v>399</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>400</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="s">
+        <v>401</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>398</v>
+      </c>
+      <c r="C8" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="E6" s="23" t="s">
-        <v>193</v>
-      </c>
-      <c r="F6" s="23" t="s">
+      <c r="D8" s="25" t="s">
+        <v>402</v>
+      </c>
+      <c r="E8" s="25" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
-        <v>387</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>384</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>288</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>389</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>391</v>
-      </c>
-      <c r="E8" s="23" t="s">
-        <v>392</v>
-      </c>
-      <c r="F8" s="23" t="s">
-        <v>186</v>
-      </c>
+      <c r="F8" s="27"/>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>393</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>390</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="A9" s="21" t="s">
+        <v>403</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>398</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="E9" s="23" t="s">
+      <c r="D9" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="F9" s="24"/>
+      <c r="F9" s="23"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
@@ -2407,200 +2796,200 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="12" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B2" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="C2" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="D2" s="21" t="s">
-        <v>395</v>
-      </c>
-      <c r="E2" s="21" t="s">
-        <v>352</v>
-      </c>
-      <c r="F2" s="21" t="s">
+      <c r="B2" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="C2" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="D2" s="10" t="s">
+        <v>405</v>
+      </c>
+      <c r="E2" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="F2" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B3" s="21" t="s">
-        <v>394</v>
-      </c>
-      <c r="C3" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>396</v>
-      </c>
-      <c r="E3" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="F3" s="21" t="s">
+      <c r="B3" s="10" t="s">
+        <v>404</v>
+      </c>
+      <c r="C3" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>406</v>
+      </c>
+      <c r="E3" s="10" t="s">
+        <v>355</v>
+      </c>
+      <c r="F3" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="B4" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="C4" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="D4" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="E4" s="21" t="s">
+      <c r="B4" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="E4" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B5" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="C5" s="21" t="s">
+      <c r="B5" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C5" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="10" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B6" s="21" t="s">
-        <v>397</v>
-      </c>
-      <c r="C6" s="21" t="s">
+      <c r="B6" s="10" t="s">
+        <v>407</v>
+      </c>
+      <c r="C6" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="E6" s="21" t="s">
-        <v>388</v>
-      </c>
-      <c r="F6" s="21" t="s">
+      <c r="E6" s="10" t="s">
+        <v>408</v>
+      </c>
+      <c r="F6" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
-        <v>398</v>
-      </c>
-      <c r="B7" s="21" t="s">
+      <c r="A7" s="10" t="s">
+        <v>409</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>399</v>
-      </c>
-      <c r="E7" s="21" t="s">
+      <c r="C7" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
-        <v>400</v>
-      </c>
-      <c r="B8" s="21" t="s">
+      <c r="A8" s="10" t="s">
+        <v>411</v>
+      </c>
+      <c r="B8" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C8" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="D8" s="21" t="s">
-        <v>344</v>
-      </c>
-      <c r="E8" s="21" t="s">
+      <c r="C8" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>345</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>401</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="A9" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="B9" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="C9" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>347</v>
-      </c>
-      <c r="E9" s="21" t="s">
+      <c r="D9" s="10" t="s">
+        <v>348</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="F9" s="25"/>
+      <c r="F9" s="17"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>402</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="A10" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>403</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>403</v>
-      </c>
-      <c r="E10" s="21" t="s">
+      <c r="C10" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="10" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2623,207 +3012,207 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="17.52"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16.27"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="17.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="16.55"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
-        <v>404</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>405</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>406</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>406</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>407</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>405</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>410</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>411</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>412</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>413</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>413</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>414</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
         <v>415</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B2" s="21" t="s">
         <v>416</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="C2" s="21" t="s">
         <v>417</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D2" s="21" t="s">
         <v>417</v>
       </c>
-      <c r="E5" s="23" t="s">
+      <c r="E2" s="21" t="s">
+        <v>418</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="s">
+        <v>419</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>416</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>420</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>421</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>422</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>423</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>424</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>425</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>426</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>427</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>428</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="23" t="s">
+      <c r="F5" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
-        <v>418</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>419</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="E6" s="23" t="s">
+      <c r="A6" s="21" t="s">
+        <v>429</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>430</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
-        <v>420</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>421</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>363</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>363</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="F6" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>431</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>432</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>364</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="D7" s="21" t="s">
+        <v>364</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>365</v>
+      </c>
+      <c r="F7" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>422</v>
-      </c>
-      <c r="B8" s="23" t="s">
+      <c r="A8" s="21" t="s">
+        <v>433</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>423</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>423</v>
-      </c>
-      <c r="E8" s="23" t="s">
+      <c r="C8" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>434</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>424</v>
-      </c>
-      <c r="B9" s="23" t="s">
+      <c r="A9" s="21" t="s">
+        <v>435</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="E9" s="23" t="s">
+      <c r="D9" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="F9" s="24"/>
+      <c r="F9" s="23"/>
     </row>
     <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>425</v>
-      </c>
-      <c r="B10" s="23" t="s">
+      <c r="A10" s="21" t="s">
+        <v>436</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="C10" s="23" t="s">
-        <v>426</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>426</v>
-      </c>
-      <c r="E10" s="23" t="s">
+      <c r="C10" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>437</v>
+      </c>
+      <c r="E10" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="21" t="s">
         <v>186</v>
       </c>
     </row>
@@ -2846,166 +3235,166 @@
   <dimension ref="A1:F8"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="19.75"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="16.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="19.75"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
         <v>274</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="C2" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>357</v>
-      </c>
-      <c r="E2" s="23" t="s">
+      <c r="C2" s="21" t="s">
         <v>358</v>
       </c>
-      <c r="F2" s="23" t="s">
+      <c r="D2" s="21" t="s">
+        <v>358</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>359</v>
+      </c>
+      <c r="F2" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
+      <c r="A3" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="C3" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>427</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>428</v>
-      </c>
-      <c r="F3" s="23" t="s">
+      <c r="C3" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>438</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>439</v>
+      </c>
+      <c r="F3" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="21" t="s">
         <v>277</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>429</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>429</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>361</v>
-      </c>
-      <c r="F4" s="23" t="s">
+      <c r="C4" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>440</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>362</v>
+      </c>
+      <c r="F4" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="C5" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="D5" s="23" t="s">
-        <v>431</v>
-      </c>
-      <c r="E5" s="23" t="s">
+      <c r="B5" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="F5" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
+      <c r="F5" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="E6" s="23" t="s">
+      <c r="B6" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="F6" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
-        <v>432</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="C7" s="23" t="s">
+      <c r="A7" s="21" t="s">
+        <v>443</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="C7" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="D7" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="E7" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="F7" s="24"/>
-    </row>
-    <row r="8" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>433</v>
-      </c>
-      <c r="B8" s="23" t="s">
-        <v>430</v>
-      </c>
-      <c r="C8" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>434</v>
-      </c>
-      <c r="E8" s="23" t="s">
+      <c r="F7" s="23"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>444</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>441</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>445</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="21" t="s">
         <v>186</v>
       </c>
     </row>
@@ -3028,225 +3417,1446 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="20.17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.67"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="20.17"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="17.67"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="20" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
-        <v>435</v>
-      </c>
-      <c r="B2" s="23" t="s">
-        <v>436</v>
-      </c>
-      <c r="C2" s="23" t="s">
-        <v>437</v>
-      </c>
-      <c r="D2" s="23" t="s">
-        <v>437</v>
-      </c>
-      <c r="E2" s="23" t="s">
-        <v>438</v>
-      </c>
-      <c r="F2" s="23" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
+        <v>446</v>
+      </c>
+      <c r="B2" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>448</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>449</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="s">
+        <v>450</v>
+      </c>
+      <c r="B3" s="21" t="s">
+        <v>447</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="D3" s="21" t="s">
+        <v>451</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>452</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>453</v>
+      </c>
+      <c r="B4" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="D4" s="21" t="s">
+        <v>371</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>455</v>
+      </c>
+      <c r="B5" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>189</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>456</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>454</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="D6" s="21" t="s">
+        <v>288</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>457</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>459</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>210</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>460</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>461</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>462</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="C9" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9" s="21" t="s">
+        <v>192</v>
+      </c>
+      <c r="E9" s="21" t="s">
+        <v>252</v>
+      </c>
+      <c r="F9" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
+        <v>463</v>
+      </c>
+      <c r="B10" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" s="21" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>190</v>
+      </c>
+      <c r="F10" s="23"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
+        <v>464</v>
+      </c>
+      <c r="B11" s="21" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>465</v>
+      </c>
+      <c r="E11" s="21" t="s">
+        <v>206</v>
+      </c>
+      <c r="F11" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F8"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="27.82"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="20" t="s">
+        <v>377</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>378</v>
+      </c>
+      <c r="D1" s="20" t="s">
+        <v>379</v>
+      </c>
+      <c r="E1" s="20" t="s">
+        <v>380</v>
+      </c>
+      <c r="F1" s="20" t="s">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="21" t="s">
+        <v>466</v>
+      </c>
+      <c r="B2" s="21" t="n">
+        <v>99</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="D2" s="28" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="F2" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>439</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>436</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>440</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>440</v>
-      </c>
-      <c r="E3" s="23" t="s">
-        <v>441</v>
-      </c>
-      <c r="F3" s="23" t="s">
-        <v>186</v>
-      </c>
+      <c r="A3" s="21" t="s">
+        <v>469</v>
+      </c>
+      <c r="B3" s="21" t="n">
+        <v>100</v>
+      </c>
+      <c r="C3" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="D3" s="28" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E3" s="21" t="s">
+        <v>470</v>
+      </c>
+      <c r="F3" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>471</v>
+      </c>
+      <c r="B4" s="21" t="n">
+        <v>101</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="D4" s="28" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="21" t="s">
+        <v>472</v>
+      </c>
+      <c r="F4" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
+        <v>473</v>
+      </c>
+      <c r="B5" s="21" t="n">
+        <v>102</v>
+      </c>
+      <c r="C5" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="D5" s="28" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>474</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>475</v>
+      </c>
+      <c r="B6" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="D6" s="28" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>476</v>
+      </c>
+      <c r="F6" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>477</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>478</v>
+      </c>
+      <c r="C7" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="D7" s="28" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="21" t="s">
+        <v>479</v>
+      </c>
+      <c r="F7" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>480</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>481</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>467</v>
+      </c>
+      <c r="D8" s="28" t="n">
+        <f aca="false">TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="E8" s="21" t="s">
+        <v>482</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F52"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="17.52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="23.5"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="25.32"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="32.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="15.58"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="24" t="s">
+        <v>177</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>178</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>179</v>
+      </c>
+      <c r="D1" s="24" t="s">
+        <v>180</v>
+      </c>
+      <c r="E1" s="24" t="s">
+        <v>181</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="25" t="s">
+        <v>483</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C2" s="25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D2" s="25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E2" s="25" t="s">
+        <v>484</v>
+      </c>
+      <c r="F2" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="25" t="s">
+        <v>485</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C3" s="25" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="E3" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F3" s="27"/>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
-        <v>442</v>
-      </c>
-      <c r="B4" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="C4" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>370</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="F4" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
-        <v>444</v>
-      </c>
-      <c r="B5" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="C5" s="23" t="s">
+      <c r="A4" s="25" t="s">
+        <v>487</v>
+      </c>
+      <c r="B4" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C4" s="25" t="s">
+        <v>192</v>
+      </c>
+      <c r="D4" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="E4" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F4" s="27"/>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="25" t="s">
+        <v>489</v>
+      </c>
+      <c r="B5" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C5" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="D5" s="25" t="s">
+        <v>195</v>
+      </c>
+      <c r="E5" s="25" t="s">
+        <v>490</v>
+      </c>
+      <c r="F5" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="25" t="s">
+        <v>491</v>
+      </c>
+      <c r="B6" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C6" s="25" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="D6" s="25" t="n">
+        <v>-5000</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>492</v>
+      </c>
+      <c r="F6" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="25" t="s">
+        <v>493</v>
+      </c>
+      <c r="B7" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C7" s="25" t="n">
+        <v>1000.5</v>
+      </c>
+      <c r="D7" s="25" t="n">
+        <v>1000.5</v>
+      </c>
+      <c r="E7" s="25" t="s">
+        <v>494</v>
+      </c>
+      <c r="F7" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="25" t="s">
+        <v>495</v>
+      </c>
+      <c r="B8" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C8" s="25" t="s">
+        <v>496</v>
+      </c>
+      <c r="D8" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E8" s="27"/>
+      <c r="F8" s="27"/>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="25" t="s">
+        <v>497</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C9" s="25" t="n">
+        <v>500</v>
+      </c>
+      <c r="D9" s="25" t="n">
+        <v>500</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>498</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="25" t="s">
+        <v>499</v>
+      </c>
+      <c r="B10" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="D10" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E10" s="27"/>
+      <c r="F10" s="27"/>
+    </row>
+    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="25" t="s">
+        <v>500</v>
+      </c>
+      <c r="B11" s="25" t="s">
+        <v>184</v>
+      </c>
+      <c r="C11" s="25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D11" s="25" t="n">
+        <v>10000</v>
+      </c>
+      <c r="E11" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="F11" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="25" t="s">
+        <v>502</v>
+      </c>
+      <c r="B12" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C12" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="D12" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="25" t="s">
+        <v>503</v>
+      </c>
+      <c r="F12" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="25" t="s">
+        <v>504</v>
+      </c>
+      <c r="B13" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C13" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="D13" s="25" t="s">
+        <v>505</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>506</v>
+      </c>
+      <c r="F13" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="25" t="s">
+        <v>507</v>
+      </c>
+      <c r="B14" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>214</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="E5" s="23" t="s">
-        <v>189</v>
-      </c>
-      <c r="F5" s="23" t="s">
+      <c r="D14" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="E14" s="25" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
-        <v>445</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="C6" s="23" t="s">
+      <c r="F14" s="27"/>
+    </row>
+    <row r="15" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="25" t="s">
+        <v>508</v>
+      </c>
+      <c r="B15" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C15" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="D15" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="E15" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F15" s="27"/>
+    </row>
+    <row r="16" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="25" t="s">
+        <v>509</v>
+      </c>
+      <c r="B16" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C16" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D16" s="25" t="s">
         <v>288</v>
       </c>
-      <c r="E6" s="23" t="s">
-        <v>388</v>
-      </c>
-      <c r="F6" s="23" t="s">
+      <c r="E16" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="F16" s="25" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
-        <v>446</v>
-      </c>
-      <c r="B7" s="23" t="s">
-        <v>447</v>
-      </c>
-      <c r="C7" s="23" t="s">
-        <v>448</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>448</v>
-      </c>
-      <c r="E7" s="23" t="s">
-        <v>210</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>449</v>
-      </c>
-      <c r="B8" s="23" t="s">
+    <row r="17" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="25" t="s">
+        <v>511</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="D17" s="25" t="s">
+        <v>110</v>
+      </c>
+      <c r="E17" s="25" t="s">
+        <v>512</v>
+      </c>
+      <c r="F17" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="25" t="s">
+        <v>513</v>
+      </c>
+      <c r="B18" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C18" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="D18" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E18" s="25" t="s">
+        <v>514</v>
+      </c>
+      <c r="F18" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="25" t="s">
+        <v>515</v>
+      </c>
+      <c r="B19" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C19" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="D19" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="E19" s="25" t="s">
+        <v>516</v>
+      </c>
+      <c r="F19" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="25" t="s">
+        <v>517</v>
+      </c>
+      <c r="B20" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="D20" s="25" t="s">
+        <v>230</v>
+      </c>
+      <c r="E20" s="25" t="s">
+        <v>518</v>
+      </c>
+      <c r="F20" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="25" t="s">
+        <v>519</v>
+      </c>
+      <c r="B21" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C21" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="D21" s="25" t="s">
+        <v>233</v>
+      </c>
+      <c r="E21" s="25" t="s">
+        <v>520</v>
+      </c>
+      <c r="F21" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="25" t="s">
+        <v>521</v>
+      </c>
+      <c r="B22" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C22" s="25" t="s">
+        <v>522</v>
+      </c>
+      <c r="D22" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E22" s="27"/>
+      <c r="F22" s="27"/>
+    </row>
+    <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="25" t="s">
+        <v>523</v>
+      </c>
+      <c r="B23" s="25" t="s">
+        <v>208</v>
+      </c>
+      <c r="C23" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="D23" s="25" t="s">
+        <v>245</v>
+      </c>
+      <c r="E23" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="F23" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="25" t="s">
+        <v>524</v>
+      </c>
+      <c r="B24" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>450</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>450</v>
-      </c>
-      <c r="E8" s="23" t="s">
+      <c r="C24" s="25" t="s">
+        <v>525</v>
+      </c>
+      <c r="D24" s="25" t="s">
+        <v>525</v>
+      </c>
+      <c r="E24" s="25" t="s">
         <v>249</v>
       </c>
-      <c r="F8" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>451</v>
-      </c>
-      <c r="B9" s="23" t="s">
+      <c r="F24" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="25" t="s">
+        <v>526</v>
+      </c>
+      <c r="B25" s="25" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C25" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="D25" s="25" t="s">
+        <v>251</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>527</v>
+      </c>
+      <c r="F25" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="25" t="s">
+        <v>528</v>
+      </c>
+      <c r="B26" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="C26" s="25" t="n">
+        <v>12345</v>
+      </c>
+      <c r="D26" s="25" t="n">
+        <v>12345</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="F26" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="25" t="s">
+        <v>529</v>
+      </c>
+      <c r="B27" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="D27" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="E27" s="25" t="s">
+        <v>530</v>
+      </c>
+      <c r="F27" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="25" t="s">
+        <v>531</v>
+      </c>
+      <c r="B28" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="D28" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" s="27"/>
+      <c r="F28" s="27"/>
+    </row>
+    <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="25" t="s">
+        <v>532</v>
+      </c>
+      <c r="B29" s="25" t="s">
+        <v>247</v>
+      </c>
+      <c r="C29" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>533</v>
+      </c>
+      <c r="E29" s="25" t="s">
+        <v>501</v>
+      </c>
+      <c r="F29" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="25" t="s">
+        <v>534</v>
+      </c>
+      <c r="B30" s="25" t="s">
+        <v>261</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="D30" s="25" t="s">
+        <v>535</v>
+      </c>
+      <c r="E30" s="25" t="s">
+        <v>536</v>
+      </c>
+      <c r="F30" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="25" t="s">
+        <v>537</v>
+      </c>
+      <c r="B31" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C31" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="E31" s="25" t="s">
+        <v>538</v>
+      </c>
+      <c r="F31" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="25" t="s">
+        <v>539</v>
+      </c>
+      <c r="B32" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="D32" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="E32" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F32" s="27"/>
+    </row>
+    <row r="33" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="25" t="s">
+        <v>540</v>
+      </c>
+      <c r="B33" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>216</v>
+      </c>
+      <c r="D33" s="25" t="s">
+        <v>488</v>
+      </c>
+      <c r="E33" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F33" s="27"/>
+    </row>
+    <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="25" t="s">
+        <v>541</v>
+      </c>
+      <c r="B34" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="D34" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="E34" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="F34" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="25" t="s">
+        <v>542</v>
+      </c>
+      <c r="B35" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="D35" s="25" t="s">
+        <v>224</v>
+      </c>
+      <c r="E35" s="25" t="s">
+        <v>543</v>
+      </c>
+      <c r="F35" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="25" t="s">
+        <v>544</v>
+      </c>
+      <c r="B36" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="D36" s="25" t="s">
+        <v>227</v>
+      </c>
+      <c r="E36" s="25" t="s">
+        <v>545</v>
+      </c>
+      <c r="F36" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="25" t="s">
+        <v>546</v>
+      </c>
+      <c r="B37" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="E37" s="25" t="s">
+        <v>547</v>
+      </c>
+      <c r="F37" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="25" t="s">
+        <v>548</v>
+      </c>
+      <c r="B38" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="C38" s="25" t="s">
+        <v>550</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>550</v>
+      </c>
+      <c r="E38" s="25" t="s">
+        <v>551</v>
+      </c>
+      <c r="F38" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="25" t="s">
+        <v>552</v>
+      </c>
+      <c r="B39" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="C39" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="D39" s="25" t="s">
+        <v>79</v>
+      </c>
+      <c r="E39" s="25" t="s">
+        <v>553</v>
+      </c>
+      <c r="F39" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="25" t="s">
+        <v>554</v>
+      </c>
+      <c r="B40" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="C40" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="D40" s="25" t="s">
+        <v>83</v>
+      </c>
+      <c r="E40" s="25" t="s">
+        <v>555</v>
+      </c>
+      <c r="F40" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="25" t="s">
+        <v>556</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="C41" s="25" t="s">
+        <v>557</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>557</v>
+      </c>
+      <c r="E41" s="25" t="s">
+        <v>558</v>
+      </c>
+      <c r="F41" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="25" t="s">
+        <v>559</v>
+      </c>
+      <c r="B42" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="C42" s="25" t="s">
+        <v>560</v>
+      </c>
+      <c r="D42" s="25" t="s">
+        <v>560</v>
+      </c>
+      <c r="E42" s="25" t="s">
+        <v>561</v>
+      </c>
+      <c r="F42" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="25" t="s">
+        <v>562</v>
+      </c>
+      <c r="B43" s="25" t="s">
+        <v>549</v>
+      </c>
+      <c r="C43" s="25" t="s">
+        <v>550</v>
+      </c>
+      <c r="D43" s="25" t="s">
+        <v>550</v>
+      </c>
+      <c r="E43" s="25" t="s">
+        <v>563</v>
+      </c>
+      <c r="F43" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="25" t="s">
+        <v>564</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>565</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="E44" s="25" t="s">
+        <v>566</v>
+      </c>
+      <c r="F44" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="25" t="s">
+        <v>567</v>
+      </c>
+      <c r="B45" s="25" t="s">
+        <v>565</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>486</v>
+      </c>
+      <c r="E45" s="25" t="s">
+        <v>190</v>
+      </c>
+      <c r="F45" s="27"/>
+    </row>
+    <row r="46" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="25" t="s">
+        <v>568</v>
+      </c>
+      <c r="B46" s="25" t="s">
+        <v>565</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>288</v>
+      </c>
+      <c r="E46" s="25" t="s">
+        <v>510</v>
+      </c>
+      <c r="F46" s="25" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="25" t="s">
+        <v>569</v>
+      </c>
+      <c r="B47" s="25" t="s">
+        <v>565</v>
+      </c>
+      <c r="C47" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="D47" s="25" t="s">
+        <v>282</v>
+      </c>
+      <c r="E47" s="25" t="s">
+        <v>570</v>
+      </c>
+      <c r="F47" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="25" t="s">
+        <v>571</v>
+      </c>
+      <c r="B48" s="25" t="s">
+        <v>572</v>
+      </c>
+      <c r="C48" s="25" t="n">
+        <v>123456</v>
+      </c>
+      <c r="D48" s="25" t="n">
+        <v>123456</v>
+      </c>
+      <c r="E48" s="25" t="s">
+        <v>185</v>
+      </c>
+      <c r="F48" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="25" t="s">
+        <v>573</v>
+      </c>
+      <c r="B49" s="25" t="s">
+        <v>572</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="D49" s="25" t="s">
+        <v>214</v>
+      </c>
+      <c r="E49" s="25" t="s">
+        <v>574</v>
+      </c>
+      <c r="F49" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="25" t="s">
+        <v>575</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>572</v>
+      </c>
+      <c r="C50" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D50" s="25" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="23" t="s">
-        <v>252</v>
-      </c>
-      <c r="F9" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>452</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="C10" s="23" t="s">
-        <v>188</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="E10" s="23" t="s">
+      <c r="E50" s="25" t="s">
+        <v>576</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="25" t="s">
+        <v>577</v>
+      </c>
+      <c r="B51" s="25" t="s">
+        <v>572</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>348</v>
+      </c>
+      <c r="D51" s="25" t="s">
         <v>190</v>
       </c>
-      <c r="F10" s="24"/>
-    </row>
-    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="s">
-        <v>453</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>247</v>
-      </c>
-      <c r="C11" s="23" t="s">
-        <v>454</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>454</v>
-      </c>
-      <c r="E11" s="23" t="s">
-        <v>206</v>
-      </c>
-      <c r="F11" s="23" t="s">
+      <c r="E51" s="27"/>
+      <c r="F51" s="27"/>
+    </row>
+    <row r="52" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="25" t="s">
+        <v>578</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>572</v>
+      </c>
+      <c r="C52" s="25" t="n">
+        <v>987654</v>
+      </c>
+      <c r="D52" s="25" t="n">
+        <v>987654</v>
+      </c>
+      <c r="E52" s="25" t="s">
+        <v>579</v>
+      </c>
+      <c r="F52" s="25" t="s">
         <v>186</v>
       </c>
     </row>
@@ -4210,1069 +5820,1069 @@
   <dimension ref="A1:F53"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="14.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.78"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.27"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.99"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="18.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="16.27"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="12" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
+      <c r="A2" s="10" t="s">
         <v>183</v>
       </c>
-      <c r="B2" s="21" t="s">
+      <c r="B2" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C2" s="21" t="n">
+      <c r="C2" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="D2" s="21" t="n">
+      <c r="D2" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="F2" s="21" t="s">
+      <c r="F2" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E3" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F3" s="21" t="s">
+      <c r="F3" s="10" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="A4" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="B4" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="C4" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="D4" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E4" s="21" t="s">
+      <c r="E4" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="F4" s="21" t="s">
+      <c r="F4" s="10" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C5" s="21" t="s">
+      <c r="C5" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="10" t="s">
         <v>195</v>
       </c>
-      <c r="E5" s="21" t="s">
+      <c r="E5" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="F5" s="21" t="s">
+      <c r="F5" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="A6" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="B6" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C6" s="21" t="n">
+      <c r="C6" s="10" t="n">
         <v>-5000</v>
       </c>
-      <c r="D6" s="21" t="n">
+      <c r="D6" s="10" t="n">
         <v>-5000</v>
       </c>
-      <c r="E6" s="21" t="s">
+      <c r="E6" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="F6" s="21" t="s">
+      <c r="F6" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="10" t="s">
         <v>200</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="B7" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C7" s="21" t="n">
+      <c r="C7" s="10" t="n">
         <v>1000.5</v>
       </c>
-      <c r="D7" s="21" t="n">
+      <c r="D7" s="10" t="n">
         <v>1000.5</v>
       </c>
-      <c r="E7" s="21" t="s">
+      <c r="E7" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="F7" s="21" t="s">
+      <c r="F7" s="10" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C8" s="21" t="n">
+      <c r="C8" s="10" t="n">
         <v>500</v>
       </c>
-      <c r="D8" s="21" t="n">
+      <c r="D8" s="10" t="n">
         <v>500</v>
       </c>
-      <c r="E8" s="21" t="s">
+      <c r="E8" s="10" t="s">
         <v>204</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="10" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
+      <c r="A9" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="B9" s="21" t="s">
+      <c r="B9" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="C9" s="21" t="n">
+      <c r="C9" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="D9" s="21" t="n">
+      <c r="D9" s="10" t="n">
         <v>10000</v>
       </c>
-      <c r="E9" s="21" t="s">
+      <c r="E9" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F9" s="21" t="s">
+      <c r="F9" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="10" t="s">
         <v>207</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C10" s="21" t="s">
+      <c r="C10" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="10" t="s">
         <v>209</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="21" t="s">
+      <c r="A11" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="B11" s="21" t="s">
+      <c r="B11" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C11" s="21" t="s">
+      <c r="C11" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E11" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="10" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="B13" s="21" t="s">
+      <c r="B13" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C13" s="21" t="s">
+      <c r="C13" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D13" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E13" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F13" s="10" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="21" t="s">
+      <c r="A14" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="B14" s="21" t="s">
+      <c r="B14" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C14" s="21" t="s">
+      <c r="C14" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="D14" s="21" t="s">
+      <c r="D14" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="E14" s="21" t="s">
+      <c r="E14" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="F14" s="21" t="s">
+      <c r="F14" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B15" s="21" t="s">
+      <c r="B15" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C15" s="21" t="s">
+      <c r="C15" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="21" t="s">
+      <c r="A16" s="10" t="s">
         <v>223</v>
       </c>
-      <c r="B16" s="21" t="s">
+      <c r="B16" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C16" s="21" t="s">
+      <c r="C16" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="D16" s="21" t="s">
+      <c r="D16" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="E16" s="21" t="s">
+      <c r="E16" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="F16" s="21" t="s">
+      <c r="F16" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="B17" s="21" t="s">
+      <c r="B17" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C17" s="21" t="s">
+      <c r="C17" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="D17" s="21" t="s">
+      <c r="D17" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="E17" s="21" t="s">
+      <c r="E17" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="10" t="s">
         <v>229</v>
       </c>
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C18" s="21" t="s">
+      <c r="C18" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="D18" s="21" t="s">
+      <c r="D18" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="E18" s="21" t="s">
+      <c r="E18" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="21" t="s">
+      <c r="A19" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="B19" s="21" t="s">
+      <c r="B19" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C19" s="21" t="s">
+      <c r="C19" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="D19" s="21" t="s">
+      <c r="D19" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E19" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B20" s="21" t="s">
+      <c r="B20" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C20" s="21" t="s">
+      <c r="C20" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="10" t="s">
         <v>236</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="21" t="s">
+      <c r="A21" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B21" s="21" t="s">
+      <c r="B21" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C21" s="21" t="s">
+      <c r="C21" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="D21" s="21" t="s">
+      <c r="D21" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="E21" s="21" t="s">
+      <c r="E21" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="B22" s="21" t="s">
+      <c r="B22" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C22" s="21" t="s">
+      <c r="C22" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D22" s="21" t="s">
+      <c r="D22" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="E22" s="21" t="s">
+      <c r="E22" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="F22" s="21" t="s">
+      <c r="F22" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="B23" s="21" t="s">
+      <c r="B23" s="10" t="s">
         <v>208</v>
       </c>
-      <c r="C23" s="21" t="s">
+      <c r="C23" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="D23" s="21" t="s">
+      <c r="D23" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="E23" s="21" t="s">
+      <c r="E23" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F23" s="21" t="s">
+      <c r="F23" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="21" t="s">
+      <c r="A24" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="B24" s="21" t="s">
+      <c r="B24" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="D24" s="21" t="s">
+      <c r="D24" s="10" t="s">
         <v>248</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="E24" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="F24" s="21" t="s">
+      <c r="F24" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="21" t="s">
+      <c r="A25" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B25" s="21" t="s">
+      <c r="B25" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C25" s="21" t="s">
+      <c r="C25" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="D25" s="21" t="s">
+      <c r="D25" s="10" t="s">
         <v>251</v>
       </c>
-      <c r="E25" s="21" t="s">
+      <c r="E25" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="F25" s="21" t="s">
+      <c r="F25" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="21" t="s">
+      <c r="A26" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B26" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C26" s="21" t="n">
+      <c r="C26" s="10" t="n">
         <v>12345</v>
       </c>
-      <c r="D26" s="21" t="n">
+      <c r="D26" s="10" t="n">
         <v>12345</v>
       </c>
-      <c r="E26" s="21" t="s">
+      <c r="E26" s="10" t="s">
         <v>254</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="F26" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="21" t="s">
+      <c r="A27" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="B27" s="21" t="s">
+      <c r="B27" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C27" s="21" t="s">
+      <c r="C27" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="D27" s="21" t="s">
+      <c r="D27" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="E27" s="21" t="s">
+      <c r="E27" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="F27" s="21" t="s">
+      <c r="F27" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="21" t="s">
+      <c r="A28" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B28" s="21" t="s">
+      <c r="B28" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C28" s="21" t="s">
+      <c r="C28" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="D28" s="21" t="s">
+      <c r="D28" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="E28" s="21" t="s">
+      <c r="E28" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F28" s="21" t="s">
+      <c r="F28" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="21" t="s">
+      <c r="A29" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="B29" s="21" t="s">
+      <c r="B29" s="10" t="s">
         <v>261</v>
       </c>
-      <c r="C29" s="21" t="s">
+      <c r="C29" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="D29" s="21" t="s">
+      <c r="D29" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="E29" s="21" t="s">
+      <c r="E29" s="10" t="s">
         <v>263</v>
       </c>
-      <c r="F29" s="21" t="s">
+      <c r="F29" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="21" t="s">
+      <c r="A30" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="B30" s="21" t="s">
+      <c r="B30" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="21" t="n">
+      <c r="C30" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="D30" s="21" t="n">
+      <c r="D30" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F30" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="21" t="s">
+      <c r="A31" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B31" s="21" t="s">
+      <c r="B31" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C31" s="21" t="s">
+      <c r="C31" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="21" t="s">
+      <c r="D31" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E31" s="21" t="s">
+      <c r="E31" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="F31" s="21" t="s">
+      <c r="F31" s="10" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
+      <c r="A32" s="10" t="s">
         <v>269</v>
       </c>
-      <c r="B32" s="21" t="s">
+      <c r="B32" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C32" s="21" t="s">
+      <c r="C32" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="D32" s="21" t="s">
+      <c r="D32" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E32" s="21" t="s">
+      <c r="E32" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="F32" s="21" t="s">
+      <c r="F32" s="10" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="21" t="s">
+      <c r="A33" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B33" s="21" t="s">
+      <c r="B33" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C33" s="21" t="n">
+      <c r="C33" s="10" t="n">
         <v>-1000</v>
       </c>
-      <c r="D33" s="21" t="n">
+      <c r="D33" s="10" t="n">
         <v>-1000</v>
       </c>
-      <c r="E33" s="21" t="s">
+      <c r="E33" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="F33" s="21" t="s">
+      <c r="F33" s="10" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="21" t="s">
+      <c r="A34" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B34" s="21" t="s">
+      <c r="B34" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="C34" s="21" t="n">
+      <c r="C34" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="D34" s="21" t="n">
+      <c r="D34" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="E34" s="21" t="s">
+      <c r="E34" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F34" s="21" t="s">
+      <c r="F34" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="s">
+      <c r="A35" s="10" t="s">
         <v>274</v>
       </c>
-      <c r="B35" s="21" t="s">
+      <c r="B35" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="C35" s="21" t="n">
+      <c r="C35" s="10" t="n">
         <v>8000</v>
       </c>
-      <c r="D35" s="21" t="n">
+      <c r="D35" s="10" t="n">
         <v>8000</v>
       </c>
-      <c r="E35" s="21" t="s">
+      <c r="E35" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="F35" s="21" t="s">
+      <c r="F35" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="21" t="s">
+      <c r="A36" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B36" s="21" t="s">
+      <c r="B36" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="C36" s="21" t="s">
+      <c r="C36" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="D36" s="21" t="s">
+      <c r="D36" s="10" t="s">
         <v>87</v>
       </c>
-      <c r="E36" s="21" t="s">
+      <c r="E36" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="F36" s="21" t="s">
+      <c r="F36" s="10" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
+      <c r="A37" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="B37" s="21" t="s">
+      <c r="B37" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="C37" s="21" t="s">
+      <c r="C37" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="D37" s="21" t="s">
+      <c r="D37" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="E37" s="21" t="s">
+      <c r="E37" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="F37" s="21" t="s">
+      <c r="F37" s="10" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="21" t="s">
+      <c r="A38" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B38" s="21" t="s">
+      <c r="B38" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="C38" s="21" t="n">
+      <c r="C38" s="10" t="n">
         <v>-3000</v>
       </c>
-      <c r="D38" s="21" t="n">
+      <c r="D38" s="10" t="n">
         <v>-3000</v>
       </c>
-      <c r="E38" s="21" t="s">
+      <c r="E38" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="F38" s="21" t="s">
+      <c r="F38" s="10" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="21" t="s">
+      <c r="A39" s="10" t="s">
         <v>279</v>
       </c>
-      <c r="B39" s="21" t="s">
+      <c r="B39" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="C39" s="21" t="n">
+      <c r="C39" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="D39" s="21" t="n">
+      <c r="D39" s="10" t="n">
         <v>5000</v>
       </c>
-      <c r="E39" s="21" t="s">
+      <c r="E39" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F39" s="21" t="s">
+      <c r="F39" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="21" t="s">
+      <c r="A40" s="10" t="s">
         <v>280</v>
       </c>
-      <c r="B40" s="21" t="s">
+      <c r="B40" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C40" s="21" t="s">
+      <c r="C40" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="D40" s="21" t="s">
+      <c r="D40" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="E40" s="21" t="s">
+      <c r="E40" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F40" s="21" t="s">
+      <c r="F40" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="21" t="s">
+      <c r="A41" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="B41" s="21" t="s">
+      <c r="B41" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C41" s="21" t="s">
+      <c r="C41" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="D41" s="21" t="s">
+      <c r="D41" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="E41" s="21" t="s">
+      <c r="E41" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="F41" s="21" t="s">
+      <c r="F41" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21" t="s">
+      <c r="A42" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B42" s="21" t="s">
+      <c r="B42" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C42" s="21" t="s">
+      <c r="C42" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="D42" s="21" t="s">
+      <c r="D42" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E42" s="21" t="s">
+      <c r="E42" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="F42" s="21" t="s">
+      <c r="F42" s="10" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="21" t="s">
+      <c r="A43" s="10" t="s">
         <v>286</v>
       </c>
-      <c r="B43" s="21" t="s">
+      <c r="B43" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C43" s="21" t="s">
+      <c r="C43" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="D43" s="21" t="s">
+      <c r="D43" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="E43" s="21" t="s">
+      <c r="E43" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="F43" s="21" t="s">
+      <c r="F43" s="10" t="s">
         <v>190</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="21" t="s">
+      <c r="A44" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="B44" s="21" t="s">
+      <c r="B44" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C44" s="21" t="s">
+      <c r="C44" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="D44" s="21" t="s">
+      <c r="D44" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="E44" s="21" t="s">
+      <c r="E44" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="F44" s="21" t="s">
+      <c r="F44" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="21" t="s">
+      <c r="A45" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="B45" s="21" t="s">
+      <c r="B45" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C45" s="21" t="s">
+      <c r="C45" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="D45" s="21" t="s">
+      <c r="D45" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="E45" s="21" t="s">
+      <c r="E45" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="F45" s="21" t="s">
+      <c r="F45" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="21" t="s">
+      <c r="A46" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B46" s="21" t="s">
+      <c r="B46" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C46" s="21" t="s">
+      <c r="C46" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="D46" s="21" t="s">
+      <c r="D46" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="E46" s="21" t="s">
+      <c r="E46" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="F46" s="21" t="s">
+      <c r="F46" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="21" t="s">
+      <c r="A47" s="10" t="s">
         <v>291</v>
       </c>
-      <c r="B47" s="21" t="s">
+      <c r="B47" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C47" s="21" t="s">
+      <c r="C47" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="D47" s="21" t="s">
+      <c r="D47" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="E47" s="21" t="s">
+      <c r="E47" s="10" t="s">
         <v>228</v>
       </c>
-      <c r="F47" s="21" t="s">
+      <c r="F47" s="10" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="21" t="s">
+      <c r="A48" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="B48" s="21" t="s">
+      <c r="B48" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C48" s="21" t="s">
+      <c r="C48" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="D48" s="21" t="s">
+      <c r="D48" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="E48" s="21" t="s">
+      <c r="E48" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="F48" s="21" t="s">
+      <c r="F48" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="21" t="s">
+      <c r="A49" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B49" s="21" t="s">
+      <c r="B49" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C49" s="21" t="s">
+      <c r="C49" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="D49" s="21" t="s">
+      <c r="D49" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="E49" s="21" t="s">
+      <c r="E49" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="F49" s="21" t="s">
+      <c r="F49" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="21" t="s">
+      <c r="A50" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="B50" s="21" t="s">
+      <c r="B50" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C50" s="21" t="s">
+      <c r="C50" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="D50" s="21" t="s">
+      <c r="D50" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="E50" s="21" t="s">
+      <c r="E50" s="10" t="s">
         <v>237</v>
       </c>
-      <c r="F50" s="21" t="s">
+      <c r="F50" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="21" t="s">
+      <c r="A51" s="10" t="s">
         <v>296</v>
       </c>
-      <c r="B51" s="21" t="s">
+      <c r="B51" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C51" s="21" t="s">
+      <c r="C51" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="D51" s="21" t="s">
+      <c r="D51" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="E51" s="21" t="s">
+      <c r="E51" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="F51" s="21" t="s">
+      <c r="F51" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="21" t="s">
+      <c r="A52" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="B52" s="21" t="s">
+      <c r="B52" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C52" s="21" t="s">
+      <c r="C52" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="D52" s="21" t="s">
+      <c r="D52" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="E52" s="21" t="s">
+      <c r="E52" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="F52" s="21" t="s">
+      <c r="F52" s="10" t="s">
         <v>197</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="21" t="s">
+      <c r="A53" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B53" s="21" t="s">
+      <c r="B53" s="10" t="s">
         <v>281</v>
       </c>
-      <c r="C53" s="21" t="s">
+      <c r="C53" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="D53" s="21" t="s">
+      <c r="D53" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="E53" s="21" t="s">
+      <c r="E53" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="F53" s="21" t="s">
+      <c r="F53" s="10" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5295,207 +6905,207 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="24.34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17.11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="26.84"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="20" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
+      <c r="A2" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="B2" s="23" t="s">
+      <c r="B2" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="D2" s="21" t="s">
         <v>301</v>
       </c>
-      <c r="E2" s="23" t="s">
+      <c r="E2" s="21" t="s">
         <v>302</v>
       </c>
-      <c r="F2" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
+      <c r="F2" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="s">
         <v>303</v>
       </c>
-      <c r="B3" s="23" t="s">
+      <c r="B3" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="C3" s="23" t="s">
+      <c r="C3" s="22" t="s">
         <v>304</v>
       </c>
-      <c r="D3" s="23" t="s">
-        <v>304</v>
-      </c>
-      <c r="E3" s="23" t="s">
+      <c r="D3" s="21" t="s">
         <v>305</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
+      <c r="E3" s="21" t="s">
         <v>306</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="F3" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
+        <v>307</v>
+      </c>
+      <c r="B4" s="21" t="s">
         <v>300</v>
       </c>
-      <c r="C4" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="D4" s="23" t="s">
-        <v>307</v>
-      </c>
-      <c r="E4" s="23" t="s">
+      <c r="C4" s="21" t="s">
         <v>308</v>
       </c>
-      <c r="F4" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
+      <c r="D4" s="21" t="s">
+        <v>308</v>
+      </c>
+      <c r="E4" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="F4" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
         <v>310</v>
       </c>
-      <c r="C5" s="23" t="s">
+      <c r="B5" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="C5" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="D5" s="21" t="s">
+        <v>312</v>
+      </c>
+      <c r="E5" s="21" t="s">
+        <v>313</v>
+      </c>
+      <c r="F5" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
+        <v>314</v>
+      </c>
+      <c r="B6" s="21" t="s">
         <v>311</v>
       </c>
-      <c r="E5" s="23" t="s">
-        <v>312</v>
-      </c>
-      <c r="F5" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
-        <v>313</v>
-      </c>
-      <c r="B6" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="C6" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="D6" s="23" t="s">
-        <v>314</v>
-      </c>
-      <c r="E6" s="23" t="s">
+      <c r="C6" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="F6" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
+      <c r="D6" s="21" t="s">
+        <v>315</v>
+      </c>
+      <c r="E6" s="21" t="s">
         <v>316</v>
       </c>
-      <c r="B7" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="C7" s="23" t="n">
+      <c r="F6" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
+        <v>317</v>
+      </c>
+      <c r="B7" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="C7" s="21" t="n">
         <v>1234567890</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D7" s="21" t="n">
         <v>1234567890</v>
       </c>
-      <c r="E7" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="F7" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
+      <c r="E7" s="21" t="s">
         <v>318</v>
       </c>
-      <c r="B8" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="C8" s="23" t="s">
+      <c r="F7" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
         <v>319</v>
       </c>
-      <c r="D8" s="23" t="s">
-        <v>319</v>
-      </c>
-      <c r="E8" s="23" t="s">
+      <c r="B8" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="C8" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>320</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>257</v>
       </c>
-      <c r="F8" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>320</v>
-      </c>
-      <c r="B9" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="C9" s="23" t="s">
+      <c r="F8" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
+        <v>321</v>
+      </c>
+      <c r="B9" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="C9" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="D9" s="23" t="s">
-        <v>321</v>
-      </c>
-      <c r="E9" s="23" t="s">
+      <c r="D9" s="21" t="s">
+        <v>322</v>
+      </c>
+      <c r="E9" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="F9" s="24"/>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>322</v>
-      </c>
-      <c r="B10" s="23" t="s">
-        <v>310</v>
-      </c>
-      <c r="C10" s="23" t="s">
+      <c r="F9" s="23"/>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
         <v>323</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>323</v>
-      </c>
-      <c r="E10" s="23" t="s">
+      <c r="B10" s="21" t="s">
+        <v>311</v>
+      </c>
+      <c r="C10" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="D10" s="21" t="s">
+        <v>324</v>
+      </c>
+      <c r="E10" s="21" t="s">
+        <v>325</v>
+      </c>
+      <c r="F10" s="21" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5518,227 +7128,227 @@
   <dimension ref="A1:F11"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="15.72"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="18.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="18.64"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="15.72"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="18.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.64"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="20" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="20" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="20" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="20" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="20" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="20" t="s">
         <v>182</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="23" t="s">
-        <v>325</v>
-      </c>
-      <c r="B2" s="23" t="s">
+      <c r="A2" s="21" t="s">
         <v>326</v>
       </c>
-      <c r="C2" s="23" t="s">
+      <c r="B2" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="D2" s="23" t="s">
+      <c r="C2" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="D2" s="21" t="s">
+        <v>328</v>
+      </c>
+      <c r="E2" s="21" t="s">
+        <v>329</v>
+      </c>
+      <c r="F2" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="21" t="s">
+        <v>330</v>
+      </c>
+      <c r="B3" s="21" t="s">
         <v>327</v>
       </c>
-      <c r="E2" s="23" t="s">
-        <v>328</v>
-      </c>
-      <c r="F2" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="23" t="s">
-        <v>329</v>
-      </c>
-      <c r="B3" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="C3" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="D3" s="23" t="s">
-        <v>330</v>
-      </c>
-      <c r="E3" s="23" t="s">
+      <c r="C3" s="21" t="s">
         <v>331</v>
       </c>
-      <c r="F3" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="23" t="s">
+      <c r="D3" s="21" t="s">
+        <v>331</v>
+      </c>
+      <c r="E3" s="21" t="s">
         <v>332</v>
       </c>
-      <c r="B4" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="C4" s="23" t="s">
+      <c r="F3" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="21" t="s">
         <v>333</v>
       </c>
-      <c r="D4" s="23" t="s">
-        <v>333</v>
-      </c>
-      <c r="E4" s="23" t="s">
+      <c r="B4" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="21" t="s">
         <v>334</v>
       </c>
-      <c r="F4" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="23" t="s">
+      <c r="D4" s="21" t="s">
+        <v>334</v>
+      </c>
+      <c r="E4" s="21" t="s">
         <v>335</v>
       </c>
-      <c r="B5" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="C5" s="23" t="s">
+      <c r="F4" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
         <v>336</v>
       </c>
-      <c r="D5" s="23" t="s">
-        <v>336</v>
-      </c>
-      <c r="E5" s="23" t="s">
+      <c r="B5" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C5" s="21" t="s">
         <v>337</v>
       </c>
-      <c r="F5" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="23" t="s">
+      <c r="D5" s="21" t="s">
+        <v>337</v>
+      </c>
+      <c r="E5" s="21" t="s">
         <v>338</v>
       </c>
-      <c r="B6" s="23" t="s">
-        <v>326</v>
-      </c>
-      <c r="C6" s="23" t="s">
+      <c r="F5" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
         <v>339</v>
       </c>
-      <c r="D6" s="23" t="s">
-        <v>339</v>
-      </c>
-      <c r="E6" s="23" t="s">
+      <c r="B6" s="21" t="s">
+        <v>327</v>
+      </c>
+      <c r="C6" s="21" t="s">
         <v>340</v>
       </c>
-      <c r="F6" s="23" t="s">
+      <c r="D6" s="21" t="s">
+        <v>340</v>
+      </c>
+      <c r="E6" s="21" t="s">
+        <v>341</v>
+      </c>
+      <c r="F6" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23" t="s">
-        <v>341</v>
-      </c>
-      <c r="B7" s="23" t="s">
+      <c r="A7" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="B7" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="C7" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="D7" s="23" t="s">
-        <v>342</v>
-      </c>
-      <c r="E7" s="23" t="s">
+      <c r="C7" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="D7" s="21" t="s">
+        <v>343</v>
+      </c>
+      <c r="E7" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="F7" s="23" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="23" t="s">
-        <v>343</v>
-      </c>
-      <c r="B8" s="23" t="s">
+      <c r="F7" s="21" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="B8" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="C8" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="D8" s="23" t="s">
-        <v>344</v>
-      </c>
-      <c r="E8" s="23" t="s">
+      <c r="C8" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>345</v>
+      </c>
+      <c r="E8" s="21" t="s">
         <v>252</v>
       </c>
-      <c r="F8" s="23" t="s">
+      <c r="F8" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="23" t="s">
-        <v>345</v>
-      </c>
-      <c r="B9" s="23" t="s">
+      <c r="A9" s="21" t="s">
+        <v>346</v>
+      </c>
+      <c r="B9" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="23" t="n">
+      <c r="C9" s="21" t="n">
         <v>12345</v>
       </c>
-      <c r="D9" s="23" t="n">
+      <c r="D9" s="21" t="n">
         <v>12345</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="F9" s="23" t="s">
+      <c r="F9" s="21" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="23" t="s">
-        <v>346</v>
-      </c>
-      <c r="B10" s="23" t="s">
+      <c r="A10" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="B10" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="C10" s="23" t="s">
+      <c r="C10" s="21" t="s">
         <v>188</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>347</v>
-      </c>
-      <c r="E10" s="23" t="s">
+      <c r="D10" s="21" t="s">
+        <v>348</v>
+      </c>
+      <c r="E10" s="21" t="s">
         <v>190</v>
       </c>
-      <c r="F10" s="24"/>
+      <c r="F10" s="23"/>
     </row>
     <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="s">
-        <v>348</v>
-      </c>
-      <c r="B11" s="23" t="s">
+      <c r="A11" s="21" t="s">
+        <v>349</v>
+      </c>
+      <c r="B11" s="21" t="s">
         <v>247</v>
       </c>
-      <c r="C11" s="23" t="s">
-        <v>349</v>
-      </c>
-      <c r="D11" s="23" t="s">
-        <v>349</v>
-      </c>
-      <c r="E11" s="23" t="s">
+      <c r="C11" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="D11" s="21" t="s">
+        <v>350</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>206</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="21" t="s">
         <v>186</v>
       </c>
     </row>
@@ -5761,209 +7371,209 @@
   <dimension ref="A1:F10"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="18.49"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="19.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="23.79"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.33"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="18.49"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="19.89"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="23.79"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="14.33"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="B1" s="20" t="s">
+      <c r="B1" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="C1" s="20" t="s">
+      <c r="C1" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="D1" s="20" t="s">
+      <c r="D1" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="E1" s="20" t="s">
+      <c r="E1" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="F1" s="20" t="s">
+      <c r="F1" s="12" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="21" t="s">
-        <v>350</v>
-      </c>
-      <c r="B2" s="21" t="s">
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="10" t="s">
         <v>351</v>
       </c>
-      <c r="C2" s="21" t="s">
+      <c r="B2" s="10" t="s">
+        <v>352</v>
+      </c>
+      <c r="C2" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="E2" s="21" t="s">
+      <c r="E2" s="10" t="s">
+        <v>353</v>
+      </c>
+      <c r="F2" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="10" t="s">
+        <v>354</v>
+      </c>
+      <c r="B3" s="10" t="s">
         <v>352</v>
       </c>
-      <c r="F2" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="3" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="21" t="s">
-        <v>353</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>351</v>
-      </c>
-      <c r="C3" s="21" t="s">
+      <c r="C3" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="D3" s="21" t="s">
+      <c r="D3" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="E3" s="21" t="s">
-        <v>354</v>
-      </c>
-      <c r="F3" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="21" t="s">
+      <c r="E3" s="10" t="s">
         <v>355</v>
       </c>
-      <c r="B4" s="21" t="s">
+      <c r="F3" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="10" t="s">
         <v>356</v>
       </c>
-      <c r="C4" s="21" t="s">
+      <c r="B4" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="D4" s="21" t="s">
+      <c r="C4" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>358</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>359</v>
+      </c>
+      <c r="F4" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="10" t="s">
+        <v>360</v>
+      </c>
+      <c r="B5" s="10" t="s">
         <v>357</v>
       </c>
-      <c r="E4" s="21" t="s">
-        <v>358</v>
-      </c>
-      <c r="F4" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="21" t="s">
-        <v>359</v>
-      </c>
-      <c r="B5" s="21" t="s">
-        <v>356</v>
-      </c>
-      <c r="C5" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="D5" s="21" t="s">
-        <v>360</v>
-      </c>
-      <c r="E5" s="21" t="s">
+      <c r="C5" s="10" t="s">
         <v>361</v>
       </c>
-      <c r="F5" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+      <c r="D5" s="10" t="s">
+        <v>361</v>
+      </c>
+      <c r="E5" s="10" t="s">
         <v>362</v>
       </c>
-      <c r="B6" s="21" t="s">
+      <c r="F5" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="10" t="s">
+        <v>363</v>
+      </c>
+      <c r="B6" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C6" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>363</v>
-      </c>
-      <c r="E6" s="21" t="s">
+      <c r="C6" s="10" t="s">
         <v>364</v>
       </c>
-      <c r="F6" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+      <c r="D6" s="10" t="s">
+        <v>364</v>
+      </c>
+      <c r="E6" s="10" t="s">
         <v>365</v>
       </c>
-      <c r="B7" s="21" t="s">
+      <c r="F6" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="10" t="s">
+        <v>366</v>
+      </c>
+      <c r="B7" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C7" s="21" t="s">
-        <v>366</v>
-      </c>
-      <c r="D7" s="21" t="s">
-        <v>366</v>
-      </c>
-      <c r="E7" s="21" t="s">
+      <c r="C7" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="F7" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="21" t="s">
+      <c r="D7" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="E7" s="10" t="s">
         <v>368</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="F7" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="C8" s="21" t="s">
+      <c r="B8" s="10" t="s">
         <v>370</v>
       </c>
-      <c r="D8" s="21" t="s">
-        <v>370</v>
-      </c>
-      <c r="E8" s="21" t="s">
+      <c r="C8" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>371</v>
+      </c>
+      <c r="E8" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F8" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="21" t="s">
-        <v>371</v>
-      </c>
-      <c r="B9" s="21" t="s">
+      <c r="F8" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="10" t="s">
         <v>372</v>
       </c>
-      <c r="C9" s="21" t="s">
+      <c r="B9" s="10" t="s">
         <v>373</v>
       </c>
-      <c r="D9" s="21" t="s">
-        <v>373</v>
-      </c>
-      <c r="E9" s="21" t="s">
+      <c r="C9" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>374</v>
+      </c>
+      <c r="E9" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="F9" s="21" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="21" t="s">
-        <v>374</v>
-      </c>
-      <c r="B10" s="21" t="s">
+      <c r="F9" s="10" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="10" t="s">
+        <v>375</v>
+      </c>
+      <c r="B10" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="C10" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="D10" s="21" t="s">
-        <v>375</v>
-      </c>
-      <c r="E10" s="21" t="s">
+      <c r="C10" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="E10" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="F10" s="21" t="s">
+      <c r="F10" s="10" t="s">
         <v>186</v>
       </c>
     </row>
